--- a/Results/Tables/Aim_2/Differential_abundance_analysis/Combined - Maaslin2 Results.xlsx
+++ b/Results/Tables/Aim_2/Differential_abundance_analysis/Combined - Maaslin2 Results.xlsx
@@ -414,7 +414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>X6f0b4058c92e83c77533a218739a0e38</t>
+          <t>6f0b4058c92e83c77533a218739a0e38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -459,7 +459,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Xe8d0f444dc3a43708bc843fd8472b381</t>
+          <t>e8d0f444dc3a43708bc843fd8472b381</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Xd926c5000a193dc8473f190e75b9fcd0</t>
+          <t>d926c5000a193dc8473f190e75b9fcd0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X7888dc681f2841bbc77d1f456dbda3d9</t>
+          <t>7888dc681f2841bbc77d1f456dbda3d9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X76214bb13d1e7d69ca2f7827e3ac12e2</t>
+          <t>76214bb13d1e7d69ca2f7827e3ac12e2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Xdc04cb67b3295173275e20a8a7a3d16a</t>
+          <t>dc04cb67b3295173275e20a8a7a3d16a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Xdd887bed9045e6e59c223bf9074e8f71</t>
+          <t>dd887bed9045e6e59c223bf9074e8f71</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X76aa915543cd876d620ebeafeb9fd767</t>
+          <t>76aa915543cd876d620ebeafeb9fd767</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -774,7 +774,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Xa55f549b9a40506a070a2fb7e8ca0726</t>
+          <t>a55f549b9a40506a070a2fb7e8ca0726</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Xa49ea569715664c78018691088f7aaac</t>
+          <t>a49ea569715664c78018691088f7aaac</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X959a41695798ad7798d39740d7e9ae19</t>
+          <t>959a41695798ad7798d39740d7e9ae19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -909,7 +909,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X5b73138c8555560a7cd45cb7bd7ca6da</t>
+          <t>5b73138c8555560a7cd45cb7bd7ca6da</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -954,7 +954,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X3d846e34d0ebbaa6096f5b1e5e8afa03</t>
+          <t>3d846e34d0ebbaa6096f5b1e5e8afa03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X7bf7ea59cac793e65c0bc293eabf44dc</t>
+          <t>7bf7ea59cac793e65c0bc293eabf44dc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1044,7 +1044,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X93f6e99ff381954b541d29cc24c2be7c</t>
+          <t>93f6e99ff381954b541d29cc24c2be7c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1089,7 +1089,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X2487d88c9966a6b0e2b87711d51811a8</t>
+          <t>2487d88c9966a6b0e2b87711d51811a8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1134,7 +1134,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Xa9625534f57e5ed4661782588cc20467</t>
+          <t>a9625534f57e5ed4661782588cc20467</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X9f05e4992392a05c38e1c790e07f3e5c</t>
+          <t>9f05e4992392a05c38e1c790e07f3e5c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1224,7 +1224,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X18f3b811ae49dad2e01b20f5f39d10a7</t>
+          <t>18f3b811ae49dad2e01b20f5f39d10a7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1269,7 +1269,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Xff241ad98176a2c70cdb70878176ca2e</t>
+          <t>ff241ad98176a2c70cdb70878176ca2e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X94adac1e5690b5aef26d6014e471f458</t>
+          <t>94adac1e5690b5aef26d6014e471f458</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1359,7 +1359,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X85c51ab58e3beec0355a935d17f0758e</t>
+          <t>85c51ab58e3beec0355a935d17f0758e</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1404,7 +1404,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X855166a7ea9905b7590e5e5fb7da7866</t>
+          <t>855166a7ea9905b7590e5e5fb7da7866</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X9f185911874fb5d5b2623b647359f33b</t>
+          <t>9f185911874fb5d5b2623b647359f33b</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1494,7 +1494,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Xfc2bf17d11280ea7e498670124f07400</t>
+          <t>fc2bf17d11280ea7e498670124f07400</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X9f05e4992392a05c38e1c790e07f3e5c</t>
+          <t>9f05e4992392a05c38e1c790e07f3e5c</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1584,7 +1584,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X1941bdf9450a85f4069a80e526137af7</t>
+          <t>1941bdf9450a85f4069a80e526137af7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Xc5a684b3dfddaa1e68d4563ea771ed15</t>
+          <t>c5a684b3dfddaa1e68d4563ea771ed15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1674,7 +1674,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X182071d231a63cae957730240a214721</t>
+          <t>182071d231a63cae957730240a214721</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1719,7 +1719,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X570cad8230542ad8f2c032a719120bee</t>
+          <t>570cad8230542ad8f2c032a719120bee</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1764,7 +1764,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X76d6be90e19a660c9a84b35fa31d801c</t>
+          <t>76d6be90e19a660c9a84b35fa31d801c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1809,7 +1809,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X6be7c1afdd690efab2c28453f0d304da</t>
+          <t>6be7c1afdd690efab2c28453f0d304da</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1854,7 +1854,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X269fea3886e14ab0acb08ade901906fd</t>
+          <t>269fea3886e14ab0acb08ade901906fd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X4c089330a0f8ccdd7dd92492808e9247</t>
+          <t>4c089330a0f8ccdd7dd92492808e9247</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1944,7 +1944,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>X988ee95161bcfd6129fddab0fda16d68</t>
+          <t>988ee95161bcfd6129fddab0fda16d68</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1989,7 +1989,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>X77be5efca77e4204775e4e828a1580db</t>
+          <t>77be5efca77e4204775e4e828a1580db</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2034,7 +2034,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>X0b2e7a7da00f71987193e385a9a4a4d1</t>
+          <t>0b2e7a7da00f71987193e385a9a4a4d1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2079,7 +2079,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Xec65ab01e974afdd946f7c025b3ceba5</t>
+          <t>ec65ab01e974afdd946f7c025b3ceba5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>X79a123f051e7c2965a46226b1d95246e</t>
+          <t>79a123f051e7c2965a46226b1d95246e</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Xd926c5000a193dc8473f190e75b9fcd0</t>
+          <t>d926c5000a193dc8473f190e75b9fcd0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Xd926c5000a193dc8473f190e75b9fcd0</t>
+          <t>d926c5000a193dc8473f190e75b9fcd0</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2259,7 +2259,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Xc44642d31840ae8b6896c0bc0f5a8802</t>
+          <t>c44642d31840ae8b6896c0bc0f5a8802</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>X93f6e99ff381954b541d29cc24c2be7c</t>
+          <t>93f6e99ff381954b541d29cc24c2be7c</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2349,7 +2349,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Xa55f549b9a40506a070a2fb7e8ca0726</t>
+          <t>a55f549b9a40506a070a2fb7e8ca0726</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2394,7 +2394,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Xf9fecdd58f0cedd3463e687ffd85ef48</t>
+          <t>f9fecdd58f0cedd3463e687ffd85ef48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2439,7 +2439,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>X4661cd41d2df6a4bf70276894e6cc779</t>
+          <t>4661cd41d2df6a4bf70276894e6cc779</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2484,7 +2484,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>X4a21bd45b5ff48f40bbcadf6930fc3ee</t>
+          <t>4a21bd45b5ff48f40bbcadf6930fc3ee</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2529,7 +2529,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Xff241ad98176a2c70cdb70878176ca2e</t>
+          <t>ff241ad98176a2c70cdb70878176ca2e</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2574,7 +2574,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>X1131f697b19dc061094f3b846b9f66a0</t>
+          <t>1131f697b19dc061094f3b846b9f66a0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2619,7 +2619,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>X6e373fe39ea68760cf9b2bf171476a55</t>
+          <t>6e373fe39ea68760cf9b2bf171476a55</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2664,7 +2664,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Xa3d1f4355f204d4d49ad2bea3b801265</t>
+          <t>a3d1f4355f204d4d49ad2bea3b801265</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2709,7 +2709,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>X8c3c2cadc6f0966f44b3f2371d81abd3</t>
+          <t>8c3c2cadc6f0966f44b3f2371d81abd3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>X194d511e554b455dac7747ef6442339f</t>
+          <t>194d511e554b455dac7747ef6442339f</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>X194d511e554b455dac7747ef6442339f</t>
+          <t>194d511e554b455dac7747ef6442339f</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2844,7 +2844,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>X5fe7ab4157717cdcf56706e5c043b959</t>
+          <t>5fe7ab4157717cdcf56706e5c043b959</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2889,7 +2889,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Xa55f549b9a40506a070a2fb7e8ca0726</t>
+          <t>a55f549b9a40506a070a2fb7e8ca0726</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>X278651ccb0f0d07cd2ab0837262dfc39</t>
+          <t>278651ccb0f0d07cd2ab0837262dfc39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>X96c7cedbae877361d087a8b39206d408</t>
+          <t>96c7cedbae877361d087a8b39206d408</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3024,7 +3024,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>X4661cd41d2df6a4bf70276894e6cc779</t>
+          <t>4661cd41d2df6a4bf70276894e6cc779</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3069,7 +3069,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>X4c8288bfbd76958c0c094d87b97650f8</t>
+          <t>4c8288bfbd76958c0c094d87b97650f8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3114,7 +3114,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Xd4dcc0bc5f5a6e517ddf472187dbc2e7</t>
+          <t>d4dcc0bc5f5a6e517ddf472187dbc2e7</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3159,7 +3159,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>X94adac1e5690b5aef26d6014e471f458</t>
+          <t>94adac1e5690b5aef26d6014e471f458</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3204,7 +3204,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Xe52994cd67774b8f72113d04a0b2c493</t>
+          <t>e52994cd67774b8f72113d04a0b2c493</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3249,7 +3249,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Xde021ed367003d69832c2a5461985f38</t>
+          <t>de021ed367003d69832c2a5461985f38</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3294,7 +3294,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>X0b2e7a7da00f71987193e385a9a4a4d1</t>
+          <t>0b2e7a7da00f71987193e385a9a4a4d1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3339,7 +3339,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>X570cad8230542ad8f2c032a719120bee</t>
+          <t>570cad8230542ad8f2c032a719120bee</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3384,7 +3384,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>X9f185911874fb5d5b2623b647359f33b</t>
+          <t>9f185911874fb5d5b2623b647359f33b</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3429,7 +3429,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>X94a45fbb634a4ae23f34d8160d95c8b7</t>
+          <t>94a45fbb634a4ae23f34d8160d95c8b7</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3474,7 +3474,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>X7ba07d9f4e22c332b04d5646fe2ea051</t>
+          <t>7ba07d9f4e22c332b04d5646fe2ea051</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3519,7 +3519,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Xce7e172e3d64bc42dddb2f4aa26e3a03</t>
+          <t>ce7e172e3d64bc42dddb2f4aa26e3a03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3564,7 +3564,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Xd3f1d99ffce8ccadfd2ee75f7b86b0c5</t>
+          <t>d3f1d99ffce8ccadfd2ee75f7b86b0c5</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3609,7 +3609,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Xd4dcc0bc5f5a6e517ddf472187dbc2e7</t>
+          <t>d4dcc0bc5f5a6e517ddf472187dbc2e7</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>X93f6e99ff381954b541d29cc24c2be7c</t>
+          <t>93f6e99ff381954b541d29cc24c2be7c</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>X8c3c2cadc6f0966f44b3f2371d81abd3</t>
+          <t>8c3c2cadc6f0966f44b3f2371d81abd3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>X57188cc28844564b611d3dd0d6e30de7</t>
+          <t>57188cc28844564b611d3dd0d6e30de7</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3789,7 +3789,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>X960b9cea75175246a62496526868a249</t>
+          <t>960b9cea75175246a62496526868a249</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3834,7 +3834,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>X84311c29ab5cf09c0720c450dc7c1a43</t>
+          <t>84311c29ab5cf09c0720c450dc7c1a43</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3879,7 +3879,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>X9c19eb9efc671777c92ee43ca21be172</t>
+          <t>9c19eb9efc671777c92ee43ca21be172</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3924,7 +3924,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>X1941bdf9450a85f4069a80e526137af7</t>
+          <t>1941bdf9450a85f4069a80e526137af7</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3969,7 +3969,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>X5fe7ab4157717cdcf56706e5c043b959</t>
+          <t>5fe7ab4157717cdcf56706e5c043b959</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>X93f6e99ff381954b541d29cc24c2be7c</t>
+          <t>93f6e99ff381954b541d29cc24c2be7c</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4059,7 +4059,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Xa0ac269acfcd16c66700762ee6340b07</t>
+          <t>a0ac269acfcd16c66700762ee6340b07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4104,7 +4104,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>X0b3590ab4de6582222af6f3565ceca0c</t>
+          <t>0b3590ab4de6582222af6f3565ceca0c</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4149,7 +4149,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>X9c19eb9efc671777c92ee43ca21be172</t>
+          <t>9c19eb9efc671777c92ee43ca21be172</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4194,7 +4194,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>X5fe7ab4157717cdcf56706e5c043b959</t>
+          <t>5fe7ab4157717cdcf56706e5c043b959</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>X959a41695798ad7798d39740d7e9ae19</t>
+          <t>959a41695798ad7798d39740d7e9ae19</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4284,7 +4284,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>X4c8288bfbd76958c0c094d87b97650f8</t>
+          <t>4c8288bfbd76958c0c094d87b97650f8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>X960b9cea75175246a62496526868a249</t>
+          <t>960b9cea75175246a62496526868a249</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4374,7 +4374,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>X6ca83bb8d84d22ff21607c96e42f4295</t>
+          <t>6ca83bb8d84d22ff21607c96e42f4295</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4419,7 +4419,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Xf3270b7f9b020567e59ec30f7d15fc14</t>
+          <t>f3270b7f9b020567e59ec30f7d15fc14</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4464,7 +4464,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Xd3f1d99ffce8ccadfd2ee75f7b86b0c5</t>
+          <t>d3f1d99ffce8ccadfd2ee75f7b86b0c5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4509,7 +4509,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>X059d6e79cba765d062053442b8ada21c</t>
+          <t>059d6e79cba765d062053442b8ada21c</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4554,7 +4554,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>X7a6db5f059c69a310d7c97e1b488fe74</t>
+          <t>7a6db5f059c69a310d7c97e1b488fe74</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4599,7 +4599,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>X5b73138c8555560a7cd45cb7bd7ca6da</t>
+          <t>5b73138c8555560a7cd45cb7bd7ca6da</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4644,7 +4644,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>X18f3b811ae49dad2e01b20f5f39d10a7</t>
+          <t>18f3b811ae49dad2e01b20f5f39d10a7</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4689,7 +4689,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Xd3f1d99ffce8ccadfd2ee75f7b86b0c5</t>
+          <t>d3f1d99ffce8ccadfd2ee75f7b86b0c5</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4734,7 +4734,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Xcbd66fa79a3e7fa1c33d29ed908de048</t>
+          <t>cbd66fa79a3e7fa1c33d29ed908de048</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4779,7 +4779,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>X9c19eb9efc671777c92ee43ca21be172</t>
+          <t>9c19eb9efc671777c92ee43ca21be172</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4824,7 +4824,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Xcb645d9e303b0e2d761969abb610d210</t>
+          <t>cb645d9e303b0e2d761969abb610d210</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4869,7 +4869,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>X2487d88c9966a6b0e2b87711d51811a8</t>
+          <t>2487d88c9966a6b0e2b87711d51811a8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4914,7 +4914,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>X74fafaec802530941890c1f49dfbf3e4</t>
+          <t>74fafaec802530941890c1f49dfbf3e4</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4959,7 +4959,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>X74fafaec802530941890c1f49dfbf3e4</t>
+          <t>74fafaec802530941890c1f49dfbf3e4</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5004,7 +5004,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>X74fafaec802530941890c1f49dfbf3e4</t>
+          <t>74fafaec802530941890c1f49dfbf3e4</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Xc43bbd203d077ba15c26090580d64d32</t>
+          <t>c43bbd203d077ba15c26090580d64d32</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5094,7 +5094,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Xc43bbd203d077ba15c26090580d64d32</t>
+          <t>c43bbd203d077ba15c26090580d64d32</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5139,7 +5139,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Xa3d1f4355f204d4d49ad2bea3b801265</t>
+          <t>a3d1f4355f204d4d49ad2bea3b801265</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5184,7 +5184,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Xc2f27e09022e99cda9f6629948f66252</t>
+          <t>c2f27e09022e99cda9f6629948f66252</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5229,7 +5229,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>X2a7ee151e83dbc4a4ac13f84a434c8c7</t>
+          <t>2a7ee151e83dbc4a4ac13f84a434c8c7</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>X86b5603a79c587d59312beef52df3409</t>
+          <t>86b5603a79c587d59312beef52df3409</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5319,7 +5319,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>X1300fb2208dcbb54d400995de3bc2eaa</t>
+          <t>1300fb2208dcbb54d400995de3bc2eaa</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5364,7 +5364,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>X1300fb2208dcbb54d400995de3bc2eaa</t>
+          <t>1300fb2208dcbb54d400995de3bc2eaa</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5409,7 +5409,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>X7a6db5f059c69a310d7c97e1b488fe74</t>
+          <t>7a6db5f059c69a310d7c97e1b488fe74</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5454,7 +5454,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>X9f79ff73dcbc3e304545d60cdbbca33b</t>
+          <t>9f79ff73dcbc3e304545d60cdbbca33b</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5499,7 +5499,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Xf247c06edb93b0f02277e395b87328aa</t>
+          <t>f247c06edb93b0f02277e395b87328aa</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5544,7 +5544,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>X86486b103104c344caa9a990b454797c</t>
+          <t>86486b103104c344caa9a990b454797c</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5589,7 +5589,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>X80a9a51ced500bf3bfbca440e0971948</t>
+          <t>80a9a51ced500bf3bfbca440e0971948</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5634,7 +5634,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Xc43bbd203d077ba15c26090580d64d32</t>
+          <t>c43bbd203d077ba15c26090580d64d32</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5679,7 +5679,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>X84b17f815f1e8767da103f96068901ec</t>
+          <t>84b17f815f1e8767da103f96068901ec</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5724,7 +5724,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>X0029d1a452fe37b0ff76a9c1da5ccf21</t>
+          <t>0029d1a452fe37b0ff76a9c1da5ccf21</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5769,7 +5769,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Xfbbeae3dceada6928b2cdc472f5d9901</t>
+          <t>fbbeae3dceada6928b2cdc472f5d9901</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5814,7 +5814,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>X6e373fe39ea68760cf9b2bf171476a55</t>
+          <t>6e373fe39ea68760cf9b2bf171476a55</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5859,7 +5859,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>X182071d231a63cae957730240a214721</t>
+          <t>182071d231a63cae957730240a214721</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5904,7 +5904,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>X96c7cedbae877361d087a8b39206d408</t>
+          <t>96c7cedbae877361d087a8b39206d408</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5949,7 +5949,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Xe0565865ef72ba498c2938b247ff36dc</t>
+          <t>e0565865ef72ba498c2938b247ff36dc</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5994,7 +5994,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Xf857e38c09d5f11ed7357057fffcc3a0</t>
+          <t>f857e38c09d5f11ed7357057fffcc3a0</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6039,7 +6039,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Xc00514d54b15725f03c323c54796a7c0</t>
+          <t>c00514d54b15725f03c323c54796a7c0</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6084,7 +6084,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>X988ee95161bcfd6129fddab0fda16d68</t>
+          <t>988ee95161bcfd6129fddab0fda16d68</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6129,7 +6129,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Xa75f6c6ef715f88994d61a440132c65b</t>
+          <t>a75f6c6ef715f88994d61a440132c65b</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>X1f9695def389854178788b2e4a8792ee</t>
+          <t>1f9695def389854178788b2e4a8792ee</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6219,7 +6219,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Xa55f549b9a40506a070a2fb7e8ca0726</t>
+          <t>a55f549b9a40506a070a2fb7e8ca0726</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6264,7 +6264,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Xcb645d9e303b0e2d761969abb610d210</t>
+          <t>cb645d9e303b0e2d761969abb610d210</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6309,7 +6309,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>X94a45fbb634a4ae23f34d8160d95c8b7</t>
+          <t>94a45fbb634a4ae23f34d8160d95c8b7</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6354,7 +6354,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>X1131f697b19dc061094f3b846b9f66a0</t>
+          <t>1131f697b19dc061094f3b846b9f66a0</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Xecb427bf4473bf2f3205b06132125d07</t>
+          <t>ecb427bf4473bf2f3205b06132125d07</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6444,7 +6444,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>X1703aefcb845a13faff8f80ea8265820</t>
+          <t>1703aefcb845a13faff8f80ea8265820</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6489,7 +6489,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Xa49ea569715664c78018691088f7aaac</t>
+          <t>a49ea569715664c78018691088f7aaac</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6534,7 +6534,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Xe0565865ef72ba498c2938b247ff36dc</t>
+          <t>e0565865ef72ba498c2938b247ff36dc</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6579,7 +6579,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>X9f185911874fb5d5b2623b647359f33b</t>
+          <t>9f185911874fb5d5b2623b647359f33b</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6624,7 +6624,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>X4a21bd45b5ff48f40bbcadf6930fc3ee</t>
+          <t>4a21bd45b5ff48f40bbcadf6930fc3ee</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6669,7 +6669,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>X0029d1a452fe37b0ff76a9c1da5ccf21</t>
+          <t>0029d1a452fe37b0ff76a9c1da5ccf21</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6714,7 +6714,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Xd3f1d99ffce8ccadfd2ee75f7b86b0c5</t>
+          <t>d3f1d99ffce8ccadfd2ee75f7b86b0c5</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6759,7 +6759,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>X79a123f051e7c2965a46226b1d95246e</t>
+          <t>79a123f051e7c2965a46226b1d95246e</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6804,7 +6804,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>X84311c29ab5cf09c0720c450dc7c1a43</t>
+          <t>84311c29ab5cf09c0720c450dc7c1a43</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6849,7 +6849,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Xfc4575c432e5f43c1eaf202f1c5816c4</t>
+          <t>fc4575c432e5f43c1eaf202f1c5816c4</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6894,7 +6894,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>X9c19eb9efc671777c92ee43ca21be172</t>
+          <t>9c19eb9efc671777c92ee43ca21be172</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6939,7 +6939,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>X9228756628ca33af7e8809e0968c79f8</t>
+          <t>9228756628ca33af7e8809e0968c79f8</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6984,7 +6984,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>X40f29bc827ddfc03d7fb5b76fb311557</t>
+          <t>40f29bc827ddfc03d7fb5b76fb311557</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7029,7 +7029,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>X40f29bc827ddfc03d7fb5b76fb311557</t>
+          <t>40f29bc827ddfc03d7fb5b76fb311557</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7074,7 +7074,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>X8ac938c2111c4dea67b9a99a3f7900bc</t>
+          <t>8ac938c2111c4dea67b9a99a3f7900bc</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7119,7 +7119,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Xce7e172e3d64bc42dddb2f4aa26e3a03</t>
+          <t>ce7e172e3d64bc42dddb2f4aa26e3a03</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7164,7 +7164,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Xfbbeae3dceada6928b2cdc472f5d9901</t>
+          <t>fbbeae3dceada6928b2cdc472f5d9901</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7209,7 +7209,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Xc2f27e09022e99cda9f6629948f66252</t>
+          <t>c2f27e09022e99cda9f6629948f66252</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7254,7 +7254,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>X194d511e554b455dac7747ef6442339f</t>
+          <t>194d511e554b455dac7747ef6442339f</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7299,7 +7299,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>X0bc4e35da130d9cb9fc1090c80011153</t>
+          <t>0bc4e35da130d9cb9fc1090c80011153</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7344,7 +7344,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Xf3e1ff3be3a6f13f24666ea97d99cd0b</t>
+          <t>f3e1ff3be3a6f13f24666ea97d99cd0b</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7389,7 +7389,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>X5fe7ab4157717cdcf56706e5c043b959</t>
+          <t>5fe7ab4157717cdcf56706e5c043b959</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7434,7 +7434,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>X00dcba6e262a3194c68f52e6af48a071</t>
+          <t>00dcba6e262a3194c68f52e6af48a071</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7479,7 +7479,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>X970c4c927d69ee41accb2c1a29f9a023</t>
+          <t>970c4c927d69ee41accb2c1a29f9a023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7524,7 +7524,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>X0b3590ab4de6582222af6f3565ceca0c</t>
+          <t>0b3590ab4de6582222af6f3565ceca0c</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7569,7 +7569,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>X0029d1a452fe37b0ff76a9c1da5ccf21</t>
+          <t>0029d1a452fe37b0ff76a9c1da5ccf21</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7614,7 +7614,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Xc71265e180d7e06bd350017b893ea44a</t>
+          <t>c71265e180d7e06bd350017b893ea44a</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7659,7 +7659,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>X6ca83bb8d84d22ff21607c96e42f4295</t>
+          <t>6ca83bb8d84d22ff21607c96e42f4295</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7704,7 +7704,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Xdc04cb67b3295173275e20a8a7a3d16a</t>
+          <t>dc04cb67b3295173275e20a8a7a3d16a</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7749,7 +7749,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Xdd887bed9045e6e59c223bf9074e8f71</t>
+          <t>dd887bed9045e6e59c223bf9074e8f71</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7794,7 +7794,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>X0b2e7a7da00f71987193e385a9a4a4d1</t>
+          <t>0b2e7a7da00f71987193e385a9a4a4d1</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7839,7 +7839,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>X76aa915543cd876d620ebeafeb9fd767</t>
+          <t>76aa915543cd876d620ebeafeb9fd767</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7884,7 +7884,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>X76aa915543cd876d620ebeafeb9fd767</t>
+          <t>76aa915543cd876d620ebeafeb9fd767</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7929,7 +7929,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Xede2e1cdf233330f3e67603862d90fd5</t>
+          <t>ede2e1cdf233330f3e67603862d90fd5</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7974,7 +7974,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>X2132a94c12039eca49c517950714e48a</t>
+          <t>2132a94c12039eca49c517950714e48a</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8019,7 +8019,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Xf247c06edb93b0f02277e395b87328aa</t>
+          <t>f247c06edb93b0f02277e395b87328aa</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -8064,7 +8064,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Xa9625534f57e5ed4661782588cc20467</t>
+          <t>a9625534f57e5ed4661782588cc20467</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>X960b9cea75175246a62496526868a249</t>
+          <t>960b9cea75175246a62496526868a249</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8154,7 +8154,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>X970d6f0c54e1e999cbdcdefc80299e2b</t>
+          <t>970d6f0c54e1e999cbdcdefc80299e2b</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8199,7 +8199,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>X3d514b698192fb4c2a0445c3498b2cfb</t>
+          <t>3d514b698192fb4c2a0445c3498b2cfb</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -8244,7 +8244,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Xc5a684b3dfddaa1e68d4563ea771ed15</t>
+          <t>c5a684b3dfddaa1e68d4563ea771ed15</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8289,7 +8289,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>X264be41ad2f4137d7cd5fefe393e1b92</t>
+          <t>264be41ad2f4137d7cd5fefe393e1b92</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8334,7 +8334,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>X4661cd41d2df6a4bf70276894e6cc779</t>
+          <t>4661cd41d2df6a4bf70276894e6cc779</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8379,7 +8379,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>X76d6be90e19a660c9a84b35fa31d801c</t>
+          <t>76d6be90e19a660c9a84b35fa31d801c</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8424,7 +8424,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>X94adac1e5690b5aef26d6014e471f458</t>
+          <t>94adac1e5690b5aef26d6014e471f458</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8469,7 +8469,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Xd039ffee9e93545befc0b24c6b1adb8a</t>
+          <t>d039ffee9e93545befc0b24c6b1adb8a</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8514,7 +8514,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Xc5a684b3dfddaa1e68d4563ea771ed15</t>
+          <t>c5a684b3dfddaa1e68d4563ea771ed15</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8559,7 +8559,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>X264be41ad2f4137d7cd5fefe393e1b92</t>
+          <t>264be41ad2f4137d7cd5fefe393e1b92</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8604,7 +8604,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Xc6faae06a70c97500e4f329b617e70b7</t>
+          <t>c6faae06a70c97500e4f329b617e70b7</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8649,7 +8649,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>X959a41695798ad7798d39740d7e9ae19</t>
+          <t>959a41695798ad7798d39740d7e9ae19</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8694,7 +8694,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>X1f9695def389854178788b2e4a8792ee</t>
+          <t>1f9695def389854178788b2e4a8792ee</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8739,7 +8739,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>X74fafaec802530941890c1f49dfbf3e4</t>
+          <t>74fafaec802530941890c1f49dfbf3e4</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8784,7 +8784,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>X68ee03666c1dd76a9a1ca298d04bc99e</t>
+          <t>68ee03666c1dd76a9a1ca298d04bc99e</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8829,7 +8829,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>X9c804f3d76b861e98e017e380f2f04df</t>
+          <t>9c804f3d76b861e98e017e380f2f04df</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8874,7 +8874,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>X7bf7ea59cac793e65c0bc293eabf44dc</t>
+          <t>7bf7ea59cac793e65c0bc293eabf44dc</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8919,7 +8919,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>X959a41695798ad7798d39740d7e9ae19</t>
+          <t>959a41695798ad7798d39740d7e9ae19</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8964,7 +8964,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>X5d1a7a11e80c627fbc98743087f309f0</t>
+          <t>5d1a7a11e80c627fbc98743087f309f0</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -9009,7 +9009,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Xce7e172e3d64bc42dddb2f4aa26e3a03</t>
+          <t>ce7e172e3d64bc42dddb2f4aa26e3a03</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -9054,7 +9054,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>X3d846e34d0ebbaa6096f5b1e5e8afa03</t>
+          <t>3d846e34d0ebbaa6096f5b1e5e8afa03</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -9099,7 +9099,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>X9d2a55480c1cd54eacfb0243d4562261</t>
+          <t>9d2a55480c1cd54eacfb0243d4562261</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -9144,7 +9144,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Xec65ab01e974afdd946f7c025b3ceba5</t>
+          <t>ec65ab01e974afdd946f7c025b3ceba5</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -9189,7 +9189,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>X1300fb2208dcbb54d400995de3bc2eaa</t>
+          <t>1300fb2208dcbb54d400995de3bc2eaa</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -9234,7 +9234,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Xac4a57c0c6ca41f976c5c914e25ed371</t>
+          <t>ac4a57c0c6ca41f976c5c914e25ed371</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -9279,7 +9279,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Xe52994cd67774b8f72113d04a0b2c493</t>
+          <t>e52994cd67774b8f72113d04a0b2c493</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9324,7 +9324,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>X7d0ccb9242c92ba67eae0552bf7c6f94</t>
+          <t>7d0ccb9242c92ba67eae0552bf7c6f94</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9369,7 +9369,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Xa49ea569715664c78018691088f7aaac</t>
+          <t>a49ea569715664c78018691088f7aaac</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9414,7 +9414,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>X86486b103104c344caa9a990b454797c</t>
+          <t>86486b103104c344caa9a990b454797c</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -9459,7 +9459,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>X80a9a51ced500bf3bfbca440e0971948</t>
+          <t>80a9a51ced500bf3bfbca440e0971948</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -9504,7 +9504,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Xde021ed367003d69832c2a5461985f38</t>
+          <t>de021ed367003d69832c2a5461985f38</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -9549,7 +9549,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Xc6b61011752152bbbc32003f5d0c5398</t>
+          <t>c6b61011752152bbbc32003f5d0c5398</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -9594,7 +9594,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Xd3f1d99ffce8ccadfd2ee75f7b86b0c5</t>
+          <t>d3f1d99ffce8ccadfd2ee75f7b86b0c5</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -9639,7 +9639,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>X84311c29ab5cf09c0720c450dc7c1a43</t>
+          <t>84311c29ab5cf09c0720c450dc7c1a43</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -9684,7 +9684,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Xd926c5000a193dc8473f190e75b9fcd0</t>
+          <t>d926c5000a193dc8473f190e75b9fcd0</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -9729,7 +9729,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>X630532cabb74720c1204579e6fe741b4</t>
+          <t>630532cabb74720c1204579e6fe741b4</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -9774,7 +9774,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Xd4dcc0bc5f5a6e517ddf472187dbc2e7</t>
+          <t>d4dcc0bc5f5a6e517ddf472187dbc2e7</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -9819,7 +9819,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Xa81bf36dba92ea8defbda21f3633f8fe</t>
+          <t>a81bf36dba92ea8defbda21f3633f8fe</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -9864,7 +9864,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>X9f05e4992392a05c38e1c790e07f3e5c</t>
+          <t>9f05e4992392a05c38e1c790e07f3e5c</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -9909,7 +9909,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>X9228756628ca33af7e8809e0968c79f8</t>
+          <t>9228756628ca33af7e8809e0968c79f8</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -9954,7 +9954,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Xc43bbd203d077ba15c26090580d64d32</t>
+          <t>c43bbd203d077ba15c26090580d64d32</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -9999,7 +9999,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>X93f6e99ff381954b541d29cc24c2be7c</t>
+          <t>93f6e99ff381954b541d29cc24c2be7c</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -10044,7 +10044,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>X8ac938c2111c4dea67b9a99a3f7900bc</t>
+          <t>8ac938c2111c4dea67b9a99a3f7900bc</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -10089,7 +10089,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>X8c3c2cadc6f0966f44b3f2371d81abd3</t>
+          <t>8c3c2cadc6f0966f44b3f2371d81abd3</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -10134,7 +10134,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Xc00514d54b15725f03c323c54796a7c0</t>
+          <t>c00514d54b15725f03c323c54796a7c0</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -10179,7 +10179,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Xfbbeae3dceada6928b2cdc472f5d9901</t>
+          <t>fbbeae3dceada6928b2cdc472f5d9901</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -10224,7 +10224,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>X94adac1e5690b5aef26d6014e471f458</t>
+          <t>94adac1e5690b5aef26d6014e471f458</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -10269,7 +10269,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>X3d846e34d0ebbaa6096f5b1e5e8afa03</t>
+          <t>3d846e34d0ebbaa6096f5b1e5e8afa03</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -10314,7 +10314,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>X970d6f0c54e1e999cbdcdefc80299e2b</t>
+          <t>970d6f0c54e1e999cbdcdefc80299e2b</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -10359,7 +10359,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>X86b5603a79c587d59312beef52df3409</t>
+          <t>86b5603a79c587d59312beef52df3409</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -10404,7 +10404,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>X9d2a55480c1cd54eacfb0243d4562261</t>
+          <t>9d2a55480c1cd54eacfb0243d4562261</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -10449,7 +10449,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>X9d2a55480c1cd54eacfb0243d4562261</t>
+          <t>9d2a55480c1cd54eacfb0243d4562261</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -10494,7 +10494,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>X9c804f3d76b861e98e017e380f2f04df</t>
+          <t>9c804f3d76b861e98e017e380f2f04df</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -10539,7 +10539,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>X9c804f3d76b861e98e017e380f2f04df</t>
+          <t>9c804f3d76b861e98e017e380f2f04df</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -10584,7 +10584,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>X00dcba6e262a3194c68f52e6af48a071</t>
+          <t>00dcba6e262a3194c68f52e6af48a071</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -10629,7 +10629,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>X269fea3886e14ab0acb08ade901906fd</t>
+          <t>269fea3886e14ab0acb08ade901906fd</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -10674,7 +10674,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>X269fea3886e14ab0acb08ade901906fd</t>
+          <t>269fea3886e14ab0acb08ade901906fd</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -10719,7 +10719,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>X278651ccb0f0d07cd2ab0837262dfc39</t>
+          <t>278651ccb0f0d07cd2ab0837262dfc39</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -10764,7 +10764,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>X84b17f815f1e8767da103f96068901ec</t>
+          <t>84b17f815f1e8767da103f96068901ec</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -10809,7 +10809,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>X1300fb2208dcbb54d400995de3bc2eaa</t>
+          <t>1300fb2208dcbb54d400995de3bc2eaa</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -10854,7 +10854,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Xf9fecdd58f0cedd3463e687ffd85ef48</t>
+          <t>f9fecdd58f0cedd3463e687ffd85ef48</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -10899,7 +10899,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>X5c7f516ff4d244a8f63e883a44267f20</t>
+          <t>5c7f516ff4d244a8f63e883a44267f20</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -10944,7 +10944,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>X80a9a51ced500bf3bfbca440e0971948</t>
+          <t>80a9a51ced500bf3bfbca440e0971948</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -10989,7 +10989,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>X1d25e5714547bb8a8f93b8364d36889e</t>
+          <t>1d25e5714547bb8a8f93b8364d36889e</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -11034,7 +11034,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>X1d25e5714547bb8a8f93b8364d36889e</t>
+          <t>1d25e5714547bb8a8f93b8364d36889e</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -11079,7 +11079,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Xc6b61011752152bbbc32003f5d0c5398</t>
+          <t>c6b61011752152bbbc32003f5d0c5398</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -11124,7 +11124,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>X6ca83bb8d84d22ff21607c96e42f4295</t>
+          <t>6ca83bb8d84d22ff21607c96e42f4295</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -11169,7 +11169,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Xdc04cb67b3295173275e20a8a7a3d16a</t>
+          <t>dc04cb67b3295173275e20a8a7a3d16a</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -11214,7 +11214,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Xe0565865ef72ba498c2938b247ff36dc</t>
+          <t>e0565865ef72ba498c2938b247ff36dc</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -11259,7 +11259,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>X6be7c1afdd690efab2c28453f0d304da</t>
+          <t>6be7c1afdd690efab2c28453f0d304da</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -11304,7 +11304,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Xa75f6c6ef715f88994d61a440132c65b</t>
+          <t>a75f6c6ef715f88994d61a440132c65b</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -11349,7 +11349,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>X5d1a7a11e80c627fbc98743087f309f0</t>
+          <t>5d1a7a11e80c627fbc98743087f309f0</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -11394,7 +11394,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Xff241ad98176a2c70cdb70878176ca2e</t>
+          <t>ff241ad98176a2c70cdb70878176ca2e</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -11439,7 +11439,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>X76d6be90e19a660c9a84b35fa31d801c</t>
+          <t>76d6be90e19a660c9a84b35fa31d801c</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -11484,7 +11484,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>X1703aefcb845a13faff8f80ea8265820</t>
+          <t>1703aefcb845a13faff8f80ea8265820</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -11529,7 +11529,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>X76aa915543cd876d620ebeafeb9fd767</t>
+          <t>76aa915543cd876d620ebeafeb9fd767</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -11574,7 +11574,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>X86486b103104c344caa9a990b454797c</t>
+          <t>86486b103104c344caa9a990b454797c</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -11619,7 +11619,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Xcb645d9e303b0e2d761969abb610d210</t>
+          <t>cb645d9e303b0e2d761969abb610d210</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -11664,7 +11664,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>X855166a7ea9905b7590e5e5fb7da7866</t>
+          <t>855166a7ea9905b7590e5e5fb7da7866</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -11709,7 +11709,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Xf3e1ff3be3a6f13f24666ea97d99cd0b</t>
+          <t>f3e1ff3be3a6f13f24666ea97d99cd0b</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -11754,7 +11754,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>X1d25e5714547bb8a8f93b8364d36889e</t>
+          <t>1d25e5714547bb8a8f93b8364d36889e</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -11799,7 +11799,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>X4c8288bfbd76958c0c094d87b97650f8</t>
+          <t>4c8288bfbd76958c0c094d87b97650f8</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -11844,7 +11844,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Xc44642d31840ae8b6896c0bc0f5a8802</t>
+          <t>c44642d31840ae8b6896c0bc0f5a8802</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -11889,7 +11889,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Xa0ac269acfcd16c66700762ee6340b07</t>
+          <t>a0ac269acfcd16c66700762ee6340b07</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -11934,7 +11934,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>X0bc4e35da130d9cb9fc1090c80011153</t>
+          <t>0bc4e35da130d9cb9fc1090c80011153</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -11979,7 +11979,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>X988ee95161bcfd6129fddab0fda16d68</t>
+          <t>988ee95161bcfd6129fddab0fda16d68</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -12024,7 +12024,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Xa0f9d2150e3f8419a6ade2e296eafb5f</t>
+          <t>a0f9d2150e3f8419a6ade2e296eafb5f</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -12069,7 +12069,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Xe52994cd67774b8f72113d04a0b2c493</t>
+          <t>e52994cd67774b8f72113d04a0b2c493</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -12114,7 +12114,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Xa965d63a2b3f783b281a48f774847f29</t>
+          <t>a965d63a2b3f783b281a48f774847f29</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -12159,7 +12159,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>X86486b103104c344caa9a990b454797c</t>
+          <t>86486b103104c344caa9a990b454797c</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -12204,7 +12204,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Xf3270b7f9b020567e59ec30f7d15fc14</t>
+          <t>f3270b7f9b020567e59ec30f7d15fc14</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -12249,7 +12249,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Xede2e1cdf233330f3e67603862d90fd5</t>
+          <t>ede2e1cdf233330f3e67603862d90fd5</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -12294,7 +12294,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>X6f0b4058c92e83c77533a218739a0e38</t>
+          <t>6f0b4058c92e83c77533a218739a0e38</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -12339,7 +12339,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>X68ee03666c1dd76a9a1ca298d04bc99e</t>
+          <t>68ee03666c1dd76a9a1ca298d04bc99e</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -12384,7 +12384,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>X4661cd41d2df6a4bf70276894e6cc779</t>
+          <t>4661cd41d2df6a4bf70276894e6cc779</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -12429,7 +12429,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Xa49ea569715664c78018691088f7aaac</t>
+          <t>a49ea569715664c78018691088f7aaac</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12474,7 +12474,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Xc00514d54b15725f03c323c54796a7c0</t>
+          <t>c00514d54b15725f03c323c54796a7c0</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -12519,7 +12519,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Xfbbeae3dceada6928b2cdc472f5d9901</t>
+          <t>fbbeae3dceada6928b2cdc472f5d9901</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -12564,7 +12564,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>X1daf7490935642942f91e007dfefa7e9</t>
+          <t>1daf7490935642942f91e007dfefa7e9</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -12609,7 +12609,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Xff241ad98176a2c70cdb70878176ca2e</t>
+          <t>ff241ad98176a2c70cdb70878176ca2e</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -12654,7 +12654,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Xa55f549b9a40506a070a2fb7e8ca0726</t>
+          <t>a55f549b9a40506a070a2fb7e8ca0726</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -12699,7 +12699,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>X9f79ff73dcbc3e304545d60cdbbca33b</t>
+          <t>9f79ff73dcbc3e304545d60cdbbca33b</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -12744,7 +12744,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>X19563b70bb3469c665c888e4685e7f99</t>
+          <t>19563b70bb3469c665c888e4685e7f99</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -12789,7 +12789,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>X570cad8230542ad8f2c032a719120bee</t>
+          <t>570cad8230542ad8f2c032a719120bee</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12834,7 +12834,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Xede2e1cdf233330f3e67603862d90fd5</t>
+          <t>ede2e1cdf233330f3e67603862d90fd5</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -12879,7 +12879,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>X68ee03666c1dd76a9a1ca298d04bc99e</t>
+          <t>68ee03666c1dd76a9a1ca298d04bc99e</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -12924,7 +12924,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Xfc2bf17d11280ea7e498670124f07400</t>
+          <t>fc2bf17d11280ea7e498670124f07400</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -12969,7 +12969,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Xf247c06edb93b0f02277e395b87328aa</t>
+          <t>f247c06edb93b0f02277e395b87328aa</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13014,7 +13014,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>X7ba07d9f4e22c332b04d5646fe2ea051</t>
+          <t>7ba07d9f4e22c332b04d5646fe2ea051</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13059,7 +13059,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>X264be41ad2f4137d7cd5fefe393e1b92</t>
+          <t>264be41ad2f4137d7cd5fefe393e1b92</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13104,7 +13104,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Xf9fecdd58f0cedd3463e687ffd85ef48</t>
+          <t>f9fecdd58f0cedd3463e687ffd85ef48</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13149,7 +13149,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>X960b9cea75175246a62496526868a249</t>
+          <t>960b9cea75175246a62496526868a249</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13194,7 +13194,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Xec65ab01e974afdd946f7c025b3ceba5</t>
+          <t>ec65ab01e974afdd946f7c025b3ceba5</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13239,7 +13239,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>X6be7c1afdd690efab2c28453f0d304da</t>
+          <t>6be7c1afdd690efab2c28453f0d304da</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13284,7 +13284,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>X79a123f051e7c2965a46226b1d95246e</t>
+          <t>79a123f051e7c2965a46226b1d95246e</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13329,7 +13329,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>X9f79ff73dcbc3e304545d60cdbbca33b</t>
+          <t>9f79ff73dcbc3e304545d60cdbbca33b</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13374,7 +13374,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>X4a21bd45b5ff48f40bbcadf6930fc3ee</t>
+          <t>4a21bd45b5ff48f40bbcadf6930fc3ee</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13419,7 +13419,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Xfc2bf17d11280ea7e498670124f07400</t>
+          <t>fc2bf17d11280ea7e498670124f07400</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13464,7 +13464,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>X1e10ca4ce57e3019886b4f75360a76fa</t>
+          <t>1e10ca4ce57e3019886b4f75360a76fa</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13509,7 +13509,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>X7888dc681f2841bbc77d1f456dbda3d9</t>
+          <t>7888dc681f2841bbc77d1f456dbda3d9</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13554,7 +13554,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Xa81bf36dba92ea8defbda21f3633f8fe</t>
+          <t>a81bf36dba92ea8defbda21f3633f8fe</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13599,7 +13599,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>X860a5e9ee39ccb39131b57de03fb5bf8</t>
+          <t>860a5e9ee39ccb39131b57de03fb5bf8</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13644,7 +13644,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>X1941bdf9450a85f4069a80e526137af7</t>
+          <t>1941bdf9450a85f4069a80e526137af7</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13689,7 +13689,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Xdd887bed9045e6e59c223bf9074e8f71</t>
+          <t>dd887bed9045e6e59c223bf9074e8f71</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13734,7 +13734,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Xec65ab01e974afdd946f7c025b3ceba5</t>
+          <t>ec65ab01e974afdd946f7c025b3ceba5</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13779,7 +13779,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>X970c4c927d69ee41accb2c1a29f9a023</t>
+          <t>970c4c927d69ee41accb2c1a29f9a023</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13824,7 +13824,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>X264be41ad2f4137d7cd5fefe393e1b92</t>
+          <t>264be41ad2f4137d7cd5fefe393e1b92</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13869,7 +13869,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>X2487d88c9966a6b0e2b87711d51811a8</t>
+          <t>2487d88c9966a6b0e2b87711d51811a8</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13914,7 +13914,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>X4c8288bfbd76958c0c094d87b97650f8</t>
+          <t>4c8288bfbd76958c0c094d87b97650f8</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13959,7 +13959,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>X4c8288bfbd76958c0c094d87b97650f8</t>
+          <t>4c8288bfbd76958c0c094d87b97650f8</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -14004,7 +14004,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>X76d6be90e19a660c9a84b35fa31d801c</t>
+          <t>76d6be90e19a660c9a84b35fa31d801c</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -14049,7 +14049,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>X988ee95161bcfd6129fddab0fda16d68</t>
+          <t>988ee95161bcfd6129fddab0fda16d68</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -14094,7 +14094,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>X1941bdf9450a85f4069a80e526137af7</t>
+          <t>1941bdf9450a85f4069a80e526137af7</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -14139,7 +14139,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>X9c804f3d76b861e98e017e380f2f04df</t>
+          <t>9c804f3d76b861e98e017e380f2f04df</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -14184,7 +14184,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>X9c19eb9efc671777c92ee43ca21be172</t>
+          <t>9c19eb9efc671777c92ee43ca21be172</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14229,7 +14229,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Xcb645d9e303b0e2d761969abb610d210</t>
+          <t>cb645d9e303b0e2d761969abb610d210</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14274,7 +14274,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Xc2f27e09022e99cda9f6629948f66252</t>
+          <t>c2f27e09022e99cda9f6629948f66252</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14319,7 +14319,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>X7bf7ea59cac793e65c0bc293eabf44dc</t>
+          <t>7bf7ea59cac793e65c0bc293eabf44dc</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14364,7 +14364,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>X1daf7490935642942f91e007dfefa7e9</t>
+          <t>1daf7490935642942f91e007dfefa7e9</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14409,7 +14409,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>X6e373fe39ea68760cf9b2bf171476a55</t>
+          <t>6e373fe39ea68760cf9b2bf171476a55</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14454,7 +14454,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>X860a5e9ee39ccb39131b57de03fb5bf8</t>
+          <t>860a5e9ee39ccb39131b57de03fb5bf8</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14499,7 +14499,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>X77be5efca77e4204775e4e828a1580db</t>
+          <t>77be5efca77e4204775e4e828a1580db</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14544,7 +14544,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Xc71265e180d7e06bd350017b893ea44a</t>
+          <t>c71265e180d7e06bd350017b893ea44a</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14589,7 +14589,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>X80a9a51ced500bf3bfbca440e0971948</t>
+          <t>80a9a51ced500bf3bfbca440e0971948</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14634,7 +14634,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Xff241ad98176a2c70cdb70878176ca2e</t>
+          <t>ff241ad98176a2c70cdb70878176ca2e</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14679,7 +14679,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>X1f9695def389854178788b2e4a8792ee</t>
+          <t>1f9695def389854178788b2e4a8792ee</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14724,7 +14724,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>X84311c29ab5cf09c0720c450dc7c1a43</t>
+          <t>84311c29ab5cf09c0720c450dc7c1a43</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14769,7 +14769,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Xd039ffee9e93545befc0b24c6b1adb8a</t>
+          <t>d039ffee9e93545befc0b24c6b1adb8a</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14814,7 +14814,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Xd039ffee9e93545befc0b24c6b1adb8a</t>
+          <t>d039ffee9e93545befc0b24c6b1adb8a</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14859,7 +14859,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>X630532cabb74720c1204579e6fe741b4</t>
+          <t>630532cabb74720c1204579e6fe741b4</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14904,7 +14904,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>X630532cabb74720c1204579e6fe741b4</t>
+          <t>630532cabb74720c1204579e6fe741b4</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14949,7 +14949,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Xfc4575c432e5f43c1eaf202f1c5816c4</t>
+          <t>fc4575c432e5f43c1eaf202f1c5816c4</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14994,7 +14994,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Xcbd66fa79a3e7fa1c33d29ed908de048</t>
+          <t>cbd66fa79a3e7fa1c33d29ed908de048</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -15039,7 +15039,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>X1a9b1bbd7d800a46e40664e26298b33b</t>
+          <t>1a9b1bbd7d800a46e40664e26298b33b</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -15084,7 +15084,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Xcb645d9e303b0e2d761969abb610d210</t>
+          <t>cb645d9e303b0e2d761969abb610d210</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -15129,7 +15129,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>X855166a7ea9905b7590e5e5fb7da7866</t>
+          <t>855166a7ea9905b7590e5e5fb7da7866</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -15174,7 +15174,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>X960b9cea75175246a62496526868a249</t>
+          <t>960b9cea75175246a62496526868a249</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -15219,7 +15219,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>X40f29bc827ddfc03d7fb5b76fb311557</t>
+          <t>40f29bc827ddfc03d7fb5b76fb311557</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -15264,7 +15264,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Xa3d1f4355f204d4d49ad2bea3b801265</t>
+          <t>a3d1f4355f204d4d49ad2bea3b801265</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -15309,7 +15309,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>X68ee03666c1dd76a9a1ca298d04bc99e</t>
+          <t>68ee03666c1dd76a9a1ca298d04bc99e</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -15354,7 +15354,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>X8ac938c2111c4dea67b9a99a3f7900bc</t>
+          <t>8ac938c2111c4dea67b9a99a3f7900bc</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -15399,7 +15399,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>X9d7e2f75c0754a3aaf6bf21a479a0046</t>
+          <t>9d7e2f75c0754a3aaf6bf21a479a0046</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -15444,7 +15444,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Xfbbeae3dceada6928b2cdc472f5d9901</t>
+          <t>fbbeae3dceada6928b2cdc472f5d9901</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -15489,7 +15489,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>X2a7ee151e83dbc4a4ac13f84a434c8c7</t>
+          <t>2a7ee151e83dbc4a4ac13f84a434c8c7</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -15534,7 +15534,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>X86b5603a79c587d59312beef52df3409</t>
+          <t>86b5603a79c587d59312beef52df3409</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -15579,7 +15579,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>X86b5603a79c587d59312beef52df3409</t>
+          <t>86b5603a79c587d59312beef52df3409</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -15624,7 +15624,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>X9d2a55480c1cd54eacfb0243d4562261</t>
+          <t>9d2a55480c1cd54eacfb0243d4562261</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -15669,7 +15669,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>X47837e1a0b06f78d52ce1faf831fec84</t>
+          <t>47837e1a0b06f78d52ce1faf831fec84</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -15714,7 +15714,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>X47837e1a0b06f78d52ce1faf831fec84</t>
+          <t>47837e1a0b06f78d52ce1faf831fec84</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -15759,7 +15759,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>X47837e1a0b06f78d52ce1faf831fec84</t>
+          <t>47837e1a0b06f78d52ce1faf831fec84</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -15804,7 +15804,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>X76214bb13d1e7d69ca2f7827e3ac12e2</t>
+          <t>76214bb13d1e7d69ca2f7827e3ac12e2</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -15849,7 +15849,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Xa0f9d2150e3f8419a6ade2e296eafb5f</t>
+          <t>a0f9d2150e3f8419a6ade2e296eafb5f</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -15894,7 +15894,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>X1e10ca4ce57e3019886b4f75360a76fa</t>
+          <t>1e10ca4ce57e3019886b4f75360a76fa</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -15939,7 +15939,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>X77be5efca77e4204775e4e828a1580db</t>
+          <t>77be5efca77e4204775e4e828a1580db</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -15984,7 +15984,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>X7d0ccb9242c92ba67eae0552bf7c6f94</t>
+          <t>7d0ccb9242c92ba67eae0552bf7c6f94</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -16029,7 +16029,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>X0b3590ab4de6582222af6f3565ceca0c</t>
+          <t>0b3590ab4de6582222af6f3565ceca0c</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -16074,7 +16074,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>X84b17f815f1e8767da103f96068901ec</t>
+          <t>84b17f815f1e8767da103f96068901ec</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -16119,7 +16119,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Xecb427bf4473bf2f3205b06132125d07</t>
+          <t>ecb427bf4473bf2f3205b06132125d07</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -16164,7 +16164,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Xecb427bf4473bf2f3205b06132125d07</t>
+          <t>ecb427bf4473bf2f3205b06132125d07</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -16209,7 +16209,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Xc5a684b3dfddaa1e68d4563ea771ed15</t>
+          <t>c5a684b3dfddaa1e68d4563ea771ed15</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -16254,7 +16254,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>X5c7f516ff4d244a8f63e883a44267f20</t>
+          <t>5c7f516ff4d244a8f63e883a44267f20</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -16299,7 +16299,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>X5c7f516ff4d244a8f63e883a44267f20</t>
+          <t>5c7f516ff4d244a8f63e883a44267f20</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -16344,7 +16344,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>X0029d1a452fe37b0ff76a9c1da5ccf21</t>
+          <t>0029d1a452fe37b0ff76a9c1da5ccf21</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -16389,7 +16389,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>X059d6e79cba765d062053442b8ada21c</t>
+          <t>059d6e79cba765d062053442b8ada21c</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -16434,7 +16434,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>X1d25e5714547bb8a8f93b8364d36889e</t>
+          <t>1d25e5714547bb8a8f93b8364d36889e</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -16479,7 +16479,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>X1d25e5714547bb8a8f93b8364d36889e</t>
+          <t>1d25e5714547bb8a8f93b8364d36889e</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -16524,7 +16524,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Xc71265e180d7e06bd350017b893ea44a</t>
+          <t>c71265e180d7e06bd350017b893ea44a</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -16569,7 +16569,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>X61d6589645d112c45ea0478e6445fa34</t>
+          <t>61d6589645d112c45ea0478e6445fa34</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -16614,7 +16614,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>X61d6589645d112c45ea0478e6445fa34</t>
+          <t>61d6589645d112c45ea0478e6445fa34</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -16659,7 +16659,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>X61d6589645d112c45ea0478e6445fa34</t>
+          <t>61d6589645d112c45ea0478e6445fa34</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -16704,7 +16704,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Xdd887bed9045e6e59c223bf9074e8f71</t>
+          <t>dd887bed9045e6e59c223bf9074e8f71</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -16749,7 +16749,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>X7a6db5f059c69a310d7c97e1b488fe74</t>
+          <t>7a6db5f059c69a310d7c97e1b488fe74</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -16794,7 +16794,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>X7a6db5f059c69a310d7c97e1b488fe74</t>
+          <t>7a6db5f059c69a310d7c97e1b488fe74</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -16839,7 +16839,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>X86486b103104c344caa9a990b454797c</t>
+          <t>86486b103104c344caa9a990b454797c</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -16884,7 +16884,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Xc6faae06a70c97500e4f329b617e70b7</t>
+          <t>c6faae06a70c97500e4f329b617e70b7</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -16929,7 +16929,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Xc6faae06a70c97500e4f329b617e70b7</t>
+          <t>c6faae06a70c97500e4f329b617e70b7</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -16974,7 +16974,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Xe0565865ef72ba498c2938b247ff36dc</t>
+          <t>e0565865ef72ba498c2938b247ff36dc</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>X94a45fbb634a4ae23f34d8160d95c8b7</t>
+          <t>94a45fbb634a4ae23f34d8160d95c8b7</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -17064,7 +17064,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>X6be7c1afdd690efab2c28453f0d304da</t>
+          <t>6be7c1afdd690efab2c28453f0d304da</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -17109,7 +17109,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Xa75f6c6ef715f88994d61a440132c65b</t>
+          <t>a75f6c6ef715f88994d61a440132c65b</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -17154,7 +17154,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Xf857e38c09d5f11ed7357057fffcc3a0</t>
+          <t>f857e38c09d5f11ed7357057fffcc3a0</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -17199,7 +17199,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Xf857e38c09d5f11ed7357057fffcc3a0</t>
+          <t>f857e38c09d5f11ed7357057fffcc3a0</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -17244,7 +17244,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Xede2e1cdf233330f3e67603862d90fd5</t>
+          <t>ede2e1cdf233330f3e67603862d90fd5</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -17289,7 +17289,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>X5d1a7a11e80c627fbc98743087f309f0</t>
+          <t>5d1a7a11e80c627fbc98743087f309f0</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -17334,7 +17334,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Xf247c06edb93b0f02277e395b87328aa</t>
+          <t>f247c06edb93b0f02277e395b87328aa</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -17379,7 +17379,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Xa9625534f57e5ed4661782588cc20467</t>
+          <t>a9625534f57e5ed4661782588cc20467</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -17424,7 +17424,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Xac4a57c0c6ca41f976c5c914e25ed371</t>
+          <t>ac4a57c0c6ca41f976c5c914e25ed371</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -17469,7 +17469,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>X1703aefcb845a13faff8f80ea8265820</t>
+          <t>1703aefcb845a13faff8f80ea8265820</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -17514,7 +17514,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Xd039ffee9e93545befc0b24c6b1adb8a</t>
+          <t>d039ffee9e93545befc0b24c6b1adb8a</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -17559,7 +17559,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Xd4dcc0bc5f5a6e517ddf472187dbc2e7</t>
+          <t>d4dcc0bc5f5a6e517ddf472187dbc2e7</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -17604,7 +17604,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>X1a9b1bbd7d800a46e40664e26298b33b</t>
+          <t>1a9b1bbd7d800a46e40664e26298b33b</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -17649,7 +17649,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>X9228756628ca33af7e8809e0968c79f8</t>
+          <t>9228756628ca33af7e8809e0968c79f8</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -17694,7 +17694,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>X40f29bc827ddfc03d7fb5b76fb311557</t>
+          <t>40f29bc827ddfc03d7fb5b76fb311557</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -17739,7 +17739,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Xc44642d31840ae8b6896c0bc0f5a8802</t>
+          <t>c44642d31840ae8b6896c0bc0f5a8802</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -17784,7 +17784,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Xc2f27e09022e99cda9f6629948f66252</t>
+          <t>c2f27e09022e99cda9f6629948f66252</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -17829,7 +17829,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Xc2f27e09022e99cda9f6629948f66252</t>
+          <t>c2f27e09022e99cda9f6629948f66252</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -17874,7 +17874,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>X2a7ee151e83dbc4a4ac13f84a434c8c7</t>
+          <t>2a7ee151e83dbc4a4ac13f84a434c8c7</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -17919,7 +17919,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>X85c51ab58e3beec0355a935d17f0758e</t>
+          <t>85c51ab58e3beec0355a935d17f0758e</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -17964,7 +17964,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>X76214bb13d1e7d69ca2f7827e3ac12e2</t>
+          <t>76214bb13d1e7d69ca2f7827e3ac12e2</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -18009,7 +18009,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Xa0f9d2150e3f8419a6ade2e296eafb5f</t>
+          <t>a0f9d2150e3f8419a6ade2e296eafb5f</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -18054,7 +18054,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>X1daf7490935642942f91e007dfefa7e9</t>
+          <t>1daf7490935642942f91e007dfefa7e9</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -18099,7 +18099,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Xde021ed367003d69832c2a5461985f38</t>
+          <t>de021ed367003d69832c2a5461985f38</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -18144,7 +18144,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>X96c7cedbae877361d087a8b39206d408</t>
+          <t>96c7cedbae877361d087a8b39206d408</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -18189,7 +18189,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Xf3270b7f9b020567e59ec30f7d15fc14</t>
+          <t>f3270b7f9b020567e59ec30f7d15fc14</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -18234,7 +18234,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Xf857e38c09d5f11ed7357057fffcc3a0</t>
+          <t>f857e38c09d5f11ed7357057fffcc3a0</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -18279,7 +18279,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Xf857e38c09d5f11ed7357057fffcc3a0</t>
+          <t>f857e38c09d5f11ed7357057fffcc3a0</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -18324,7 +18324,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>X84b17f815f1e8767da103f96068901ec</t>
+          <t>84b17f815f1e8767da103f96068901ec</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -18369,7 +18369,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Xecb427bf4473bf2f3205b06132125d07</t>
+          <t>ecb427bf4473bf2f3205b06132125d07</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -18414,7 +18414,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Xcbd66fa79a3e7fa1c33d29ed908de048</t>
+          <t>cbd66fa79a3e7fa1c33d29ed908de048</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -18459,7 +18459,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Xcbd66fa79a3e7fa1c33d29ed908de048</t>
+          <t>cbd66fa79a3e7fa1c33d29ed908de048</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -18504,7 +18504,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>X860a5e9ee39ccb39131b57de03fb5bf8</t>
+          <t>860a5e9ee39ccb39131b57de03fb5bf8</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -18549,7 +18549,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>X9f05e4992392a05c38e1c790e07f3e5c</t>
+          <t>9f05e4992392a05c38e1c790e07f3e5c</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -18594,7 +18594,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>X855166a7ea9905b7590e5e5fb7da7866</t>
+          <t>855166a7ea9905b7590e5e5fb7da7866</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -18639,7 +18639,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>X7888dc681f2841bbc77d1f456dbda3d9</t>
+          <t>7888dc681f2841bbc77d1f456dbda3d9</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -18684,7 +18684,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>X40f29bc827ddfc03d7fb5b76fb311557</t>
+          <t>40f29bc827ddfc03d7fb5b76fb311557</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -18729,7 +18729,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>X18f3b811ae49dad2e01b20f5f39d10a7</t>
+          <t>18f3b811ae49dad2e01b20f5f39d10a7</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -18774,7 +18774,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>X8c3c2cadc6f0966f44b3f2371d81abd3</t>
+          <t>8c3c2cadc6f0966f44b3f2371d81abd3</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -18819,7 +18819,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>X19563b70bb3469c665c888e4685e7f99</t>
+          <t>19563b70bb3469c665c888e4685e7f99</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -18864,7 +18864,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>X988ee95161bcfd6129fddab0fda16d68</t>
+          <t>988ee95161bcfd6129fddab0fda16d68</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -18909,7 +18909,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>X970d6f0c54e1e999cbdcdefc80299e2b</t>
+          <t>970d6f0c54e1e999cbdcdefc80299e2b</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -18954,7 +18954,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>X5fe7ab4157717cdcf56706e5c043b959</t>
+          <t>5fe7ab4157717cdcf56706e5c043b959</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -18999,7 +18999,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>X85c51ab58e3beec0355a935d17f0758e</t>
+          <t>85c51ab58e3beec0355a935d17f0758e</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -19044,7 +19044,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>X3d514b698192fb4c2a0445c3498b2cfb</t>
+          <t>3d514b698192fb4c2a0445c3498b2cfb</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -19089,7 +19089,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>X1daf7490935642942f91e007dfefa7e9</t>
+          <t>1daf7490935642942f91e007dfefa7e9</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -19134,7 +19134,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>X1e10ca4ce57e3019886b4f75360a76fa</t>
+          <t>1e10ca4ce57e3019886b4f75360a76fa</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -19179,7 +19179,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Xe52994cd67774b8f72113d04a0b2c493</t>
+          <t>e52994cd67774b8f72113d04a0b2c493</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -19224,7 +19224,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>X00dcba6e262a3194c68f52e6af48a071</t>
+          <t>00dcba6e262a3194c68f52e6af48a071</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -19269,7 +19269,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>X7d0ccb9242c92ba67eae0552bf7c6f94</t>
+          <t>7d0ccb9242c92ba67eae0552bf7c6f94</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -19314,7 +19314,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>X970c4c927d69ee41accb2c1a29f9a023</t>
+          <t>970c4c927d69ee41accb2c1a29f9a023</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -19359,7 +19359,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>X0b3590ab4de6582222af6f3565ceca0c</t>
+          <t>0b3590ab4de6582222af6f3565ceca0c</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -19404,7 +19404,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>X269fea3886e14ab0acb08ade901906fd</t>
+          <t>269fea3886e14ab0acb08ade901906fd</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -19449,7 +19449,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>X278651ccb0f0d07cd2ab0837262dfc39</t>
+          <t>278651ccb0f0d07cd2ab0837262dfc39</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -19494,7 +19494,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Xf9fecdd58f0cedd3463e687ffd85ef48</t>
+          <t>f9fecdd58f0cedd3463e687ffd85ef48</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -19539,7 +19539,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Xf9fecdd58f0cedd3463e687ffd85ef48</t>
+          <t>f9fecdd58f0cedd3463e687ffd85ef48</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -19584,7 +19584,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Xa965d63a2b3f783b281a48f774847f29</t>
+          <t>a965d63a2b3f783b281a48f774847f29</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -19629,7 +19629,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>X80a9a51ced500bf3bfbca440e0971948</t>
+          <t>80a9a51ced500bf3bfbca440e0971948</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -19674,7 +19674,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Xc71265e180d7e06bd350017b893ea44a</t>
+          <t>c71265e180d7e06bd350017b893ea44a</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -19719,7 +19719,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>X182071d231a63cae957730240a214721</t>
+          <t>182071d231a63cae957730240a214721</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -19764,7 +19764,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>X96c7cedbae877361d087a8b39206d408</t>
+          <t>96c7cedbae877361d087a8b39206d408</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -19809,7 +19809,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>X0b2e7a7da00f71987193e385a9a4a4d1</t>
+          <t>0b2e7a7da00f71987193e385a9a4a4d1</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -19854,7 +19854,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>X9f185911874fb5d5b2623b647359f33b</t>
+          <t>9f185911874fb5d5b2623b647359f33b</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -19899,7 +19899,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Xe0565865ef72ba498c2938b247ff36dc</t>
+          <t>e0565865ef72ba498c2938b247ff36dc</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -19944,7 +19944,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>X94a45fbb634a4ae23f34d8160d95c8b7</t>
+          <t>94a45fbb634a4ae23f34d8160d95c8b7</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -19989,7 +19989,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Xf3270b7f9b020567e59ec30f7d15fc14</t>
+          <t>f3270b7f9b020567e59ec30f7d15fc14</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -20034,7 +20034,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>X6be7c1afdd690efab2c28453f0d304da</t>
+          <t>6be7c1afdd690efab2c28453f0d304da</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -20079,7 +20079,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>X4a21bd45b5ff48f40bbcadf6930fc3ee</t>
+          <t>4a21bd45b5ff48f40bbcadf6930fc3ee</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -20124,7 +20124,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>X5d1a7a11e80c627fbc98743087f309f0</t>
+          <t>5d1a7a11e80c627fbc98743087f309f0</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -20169,7 +20169,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>X1703aefcb845a13faff8f80ea8265820</t>
+          <t>1703aefcb845a13faff8f80ea8265820</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -20214,7 +20214,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>X630532cabb74720c1204579e6fe741b4</t>
+          <t>630532cabb74720c1204579e6fe741b4</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -20259,7 +20259,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>X1a9b1bbd7d800a46e40664e26298b33b</t>
+          <t>1a9b1bbd7d800a46e40664e26298b33b</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -20304,7 +20304,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>X7888dc681f2841bbc77d1f456dbda3d9</t>
+          <t>7888dc681f2841bbc77d1f456dbda3d9</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -20349,7 +20349,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>X6f0b4058c92e83c77533a218739a0e38</t>
+          <t>6f0b4058c92e83c77533a218739a0e38</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -20394,7 +20394,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>X9d7e2f75c0754a3aaf6bf21a479a0046</t>
+          <t>9d7e2f75c0754a3aaf6bf21a479a0046</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -20439,7 +20439,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>X0bc4e35da130d9cb9fc1090c80011153</t>
+          <t>0bc4e35da130d9cb9fc1090c80011153</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -20484,7 +20484,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>X61d6589645d112c45ea0478e6445fa34</t>
+          <t>61d6589645d112c45ea0478e6445fa34</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -20529,7 +20529,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>X182071d231a63cae957730240a214721</t>
+          <t>182071d231a63cae957730240a214721</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -20574,7 +20574,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Xde021ed367003d69832c2a5461985f38</t>
+          <t>de021ed367003d69832c2a5461985f38</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -20619,7 +20619,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Xc6b61011752152bbbc32003f5d0c5398</t>
+          <t>c6b61011752152bbbc32003f5d0c5398</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -20664,7 +20664,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Xdc04cb67b3295173275e20a8a7a3d16a</t>
+          <t>dc04cb67b3295173275e20a8a7a3d16a</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -20709,7 +20709,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>X2132a94c12039eca49c517950714e48a</t>
+          <t>2132a94c12039eca49c517950714e48a</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -20754,7 +20754,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>X5d1a7a11e80c627fbc98743087f309f0</t>
+          <t>5d1a7a11e80c627fbc98743087f309f0</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -20799,7 +20799,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Xd039ffee9e93545befc0b24c6b1adb8a</t>
+          <t>d039ffee9e93545befc0b24c6b1adb8a</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -20844,7 +20844,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Xac4a57c0c6ca41f976c5c914e25ed371</t>
+          <t>ac4a57c0c6ca41f976c5c914e25ed371</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -20889,7 +20889,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>X327e928d80b137060bd55c0515d64b2a</t>
+          <t>327e928d80b137060bd55c0515d64b2a</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -20934,7 +20934,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>X630532cabb74720c1204579e6fe741b4</t>
+          <t>630532cabb74720c1204579e6fe741b4</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -20979,7 +20979,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>X1f9695def389854178788b2e4a8792ee</t>
+          <t>1f9695def389854178788b2e4a8792ee</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -21024,7 +21024,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Xd926c5000a193dc8473f190e75b9fcd0</t>
+          <t>d926c5000a193dc8473f190e75b9fcd0</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -21069,7 +21069,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>X5b73138c8555560a7cd45cb7bd7ca6da</t>
+          <t>5b73138c8555560a7cd45cb7bd7ca6da</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -21114,7 +21114,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>X970c4c927d69ee41accb2c1a29f9a023</t>
+          <t>970c4c927d69ee41accb2c1a29f9a023</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -21159,7 +21159,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>X570cad8230542ad8f2c032a719120bee</t>
+          <t>570cad8230542ad8f2c032a719120bee</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -21204,7 +21204,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>X9f79ff73dcbc3e304545d60cdbbca33b</t>
+          <t>9f79ff73dcbc3e304545d60cdbbca33b</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -21249,7 +21249,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Xa75f6c6ef715f88994d61a440132c65b</t>
+          <t>a75f6c6ef715f88994d61a440132c65b</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -21294,7 +21294,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Xac4a57c0c6ca41f976c5c914e25ed371</t>
+          <t>ac4a57c0c6ca41f976c5c914e25ed371</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -21339,7 +21339,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>X2487d88c9966a6b0e2b87711d51811a8</t>
+          <t>2487d88c9966a6b0e2b87711d51811a8</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -21384,7 +21384,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>X2487d88c9966a6b0e2b87711d51811a8</t>
+          <t>2487d88c9966a6b0e2b87711d51811a8</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -21429,7 +21429,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>X7888dc681f2841bbc77d1f456dbda3d9</t>
+          <t>7888dc681f2841bbc77d1f456dbda3d9</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -21474,7 +21474,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Xa0ac269acfcd16c66700762ee6340b07</t>
+          <t>a0ac269acfcd16c66700762ee6340b07</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -21519,7 +21519,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>X8c3c2cadc6f0966f44b3f2371d81abd3</t>
+          <t>8c3c2cadc6f0966f44b3f2371d81abd3</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -21564,7 +21564,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>X3d846e34d0ebbaa6096f5b1e5e8afa03</t>
+          <t>3d846e34d0ebbaa6096f5b1e5e8afa03</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -21609,7 +21609,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>X3d514b698192fb4c2a0445c3498b2cfb</t>
+          <t>3d514b698192fb4c2a0445c3498b2cfb</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -21654,7 +21654,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>X970c4c927d69ee41accb2c1a29f9a023</t>
+          <t>970c4c927d69ee41accb2c1a29f9a023</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -21699,7 +21699,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>X959a41695798ad7798d39740d7e9ae19</t>
+          <t>959a41695798ad7798d39740d7e9ae19</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -21744,7 +21744,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>X2132a94c12039eca49c517950714e48a</t>
+          <t>2132a94c12039eca49c517950714e48a</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -21789,7 +21789,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Xa9625534f57e5ed4661782588cc20467</t>
+          <t>a9625534f57e5ed4661782588cc20467</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -21834,7 +21834,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>X1f9695def389854178788b2e4a8792ee</t>
+          <t>1f9695def389854178788b2e4a8792ee</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -21879,7 +21879,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Xd4dcc0bc5f5a6e517ddf472187dbc2e7</t>
+          <t>d4dcc0bc5f5a6e517ddf472187dbc2e7</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -21924,7 +21924,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Xa81bf36dba92ea8defbda21f3633f8fe</t>
+          <t>a81bf36dba92ea8defbda21f3633f8fe</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -21969,7 +21969,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>X4c089330a0f8ccdd7dd92492808e9247</t>
+          <t>4c089330a0f8ccdd7dd92492808e9247</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -22014,7 +22014,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>X5b73138c8555560a7cd45cb7bd7ca6da</t>
+          <t>5b73138c8555560a7cd45cb7bd7ca6da</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -22059,7 +22059,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>X74fafaec802530941890c1f49dfbf3e4</t>
+          <t>74fafaec802530941890c1f49dfbf3e4</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -22104,7 +22104,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>X9228756628ca33af7e8809e0968c79f8</t>
+          <t>9228756628ca33af7e8809e0968c79f8</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -22149,7 +22149,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Xc43bbd203d077ba15c26090580d64d32</t>
+          <t>c43bbd203d077ba15c26090580d64d32</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -22194,7 +22194,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>X68ee03666c1dd76a9a1ca298d04bc99e</t>
+          <t>68ee03666c1dd76a9a1ca298d04bc99e</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -22239,7 +22239,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>X8ac938c2111c4dea67b9a99a3f7900bc</t>
+          <t>8ac938c2111c4dea67b9a99a3f7900bc</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -22284,7 +22284,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>X9d7e2f75c0754a3aaf6bf21a479a0046</t>
+          <t>9d7e2f75c0754a3aaf6bf21a479a0046</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -22329,7 +22329,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>X1131f697b19dc061094f3b846b9f66a0</t>
+          <t>1131f697b19dc061094f3b846b9f66a0</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -22374,7 +22374,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>X0bc4e35da130d9cb9fc1090c80011153</t>
+          <t>0bc4e35da130d9cb9fc1090c80011153</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -22419,7 +22419,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>X0bc4e35da130d9cb9fc1090c80011153</t>
+          <t>0bc4e35da130d9cb9fc1090c80011153</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -22464,7 +22464,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>X970d6f0c54e1e999cbdcdefc80299e2b</t>
+          <t>970d6f0c54e1e999cbdcdefc80299e2b</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -22509,7 +22509,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>X76214bb13d1e7d69ca2f7827e3ac12e2</t>
+          <t>76214bb13d1e7d69ca2f7827e3ac12e2</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -22554,7 +22554,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>X00dcba6e262a3194c68f52e6af48a071</t>
+          <t>00dcba6e262a3194c68f52e6af48a071</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -22599,7 +22599,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Xec65ab01e974afdd946f7c025b3ceba5</t>
+          <t>ec65ab01e974afdd946f7c025b3ceba5</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -22644,7 +22644,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>X7d0ccb9242c92ba67eae0552bf7c6f94</t>
+          <t>7d0ccb9242c92ba67eae0552bf7c6f94</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -22689,7 +22689,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>X84b17f815f1e8767da103f96068901ec</t>
+          <t>84b17f815f1e8767da103f96068901ec</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -22734,7 +22734,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Xc5a684b3dfddaa1e68d4563ea771ed15</t>
+          <t>c5a684b3dfddaa1e68d4563ea771ed15</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -22779,7 +22779,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>X059d6e79cba765d062053442b8ada21c</t>
+          <t>059d6e79cba765d062053442b8ada21c</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -22824,7 +22824,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Xc6b61011752152bbbc32003f5d0c5398</t>
+          <t>c6b61011752152bbbc32003f5d0c5398</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -22869,7 +22869,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>X6ca83bb8d84d22ff21607c96e42f4295</t>
+          <t>6ca83bb8d84d22ff21607c96e42f4295</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -22914,7 +22914,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>X6ca83bb8d84d22ff21607c96e42f4295</t>
+          <t>6ca83bb8d84d22ff21607c96e42f4295</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -22959,7 +22959,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>X57188cc28844564b611d3dd0d6e30de7</t>
+          <t>57188cc28844564b611d3dd0d6e30de7</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -23004,7 +23004,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Xc6faae06a70c97500e4f329b617e70b7</t>
+          <t>c6faae06a70c97500e4f329b617e70b7</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -23049,7 +23049,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Xa75f6c6ef715f88994d61a440132c65b</t>
+          <t>a75f6c6ef715f88994d61a440132c65b</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -23094,7 +23094,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>X327e928d80b137060bd55c0515d64b2a</t>
+          <t>327e928d80b137060bd55c0515d64b2a</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -23139,7 +23139,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Xede2e1cdf233330f3e67603862d90fd5</t>
+          <t>ede2e1cdf233330f3e67603862d90fd5</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -23184,7 +23184,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Xf247c06edb93b0f02277e395b87328aa</t>
+          <t>f247c06edb93b0f02277e395b87328aa</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -23229,7 +23229,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>X9228756628ca33af7e8809e0968c79f8</t>
+          <t>9228756628ca33af7e8809e0968c79f8</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -23274,7 +23274,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>X9d7e2f75c0754a3aaf6bf21a479a0046</t>
+          <t>9d7e2f75c0754a3aaf6bf21a479a0046</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -23319,7 +23319,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Xde021ed367003d69832c2a5461985f38</t>
+          <t>de021ed367003d69832c2a5461985f38</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -23364,7 +23364,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>X3d846e34d0ebbaa6096f5b1e5e8afa03</t>
+          <t>3d846e34d0ebbaa6096f5b1e5e8afa03</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -23409,7 +23409,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>X7ba07d9f4e22c332b04d5646fe2ea051</t>
+          <t>7ba07d9f4e22c332b04d5646fe2ea051</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -23454,7 +23454,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>X194d511e554b455dac7747ef6442339f</t>
+          <t>194d511e554b455dac7747ef6442339f</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -23499,7 +23499,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Xdd887bed9045e6e59c223bf9074e8f71</t>
+          <t>dd887bed9045e6e59c223bf9074e8f71</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -23544,7 +23544,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>X4a21bd45b5ff48f40bbcadf6930fc3ee</t>
+          <t>4a21bd45b5ff48f40bbcadf6930fc3ee</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -23589,7 +23589,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Xcbd66fa79a3e7fa1c33d29ed908de048</t>
+          <t>cbd66fa79a3e7fa1c33d29ed908de048</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -23634,7 +23634,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Xa0ac269acfcd16c66700762ee6340b07</t>
+          <t>a0ac269acfcd16c66700762ee6340b07</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -23679,7 +23679,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>X9c804f3d76b861e98e017e380f2f04df</t>
+          <t>9c804f3d76b861e98e017e380f2f04df</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -23724,7 +23724,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>X85c51ab58e3beec0355a935d17f0758e</t>
+          <t>85c51ab58e3beec0355a935d17f0758e</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -23769,7 +23769,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Xc6faae06a70c97500e4f329b617e70b7</t>
+          <t>c6faae06a70c97500e4f329b617e70b7</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -23814,7 +23814,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>X0029d1a452fe37b0ff76a9c1da5ccf21</t>
+          <t>0029d1a452fe37b0ff76a9c1da5ccf21</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -23859,7 +23859,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>X327e928d80b137060bd55c0515d64b2a</t>
+          <t>327e928d80b137060bd55c0515d64b2a</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -23904,7 +23904,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>X4661cd41d2df6a4bf70276894e6cc779</t>
+          <t>4661cd41d2df6a4bf70276894e6cc779</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -23949,7 +23949,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>X79a123f051e7c2965a46226b1d95246e</t>
+          <t>79a123f051e7c2965a46226b1d95246e</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -23994,7 +23994,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>X1131f697b19dc061094f3b846b9f66a0</t>
+          <t>1131f697b19dc061094f3b846b9f66a0</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -24039,7 +24039,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>X5c7f516ff4d244a8f63e883a44267f20</t>
+          <t>5c7f516ff4d244a8f63e883a44267f20</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -24084,7 +24084,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>X264be41ad2f4137d7cd5fefe393e1b92</t>
+          <t>264be41ad2f4137d7cd5fefe393e1b92</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -24129,7 +24129,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>X327e928d80b137060bd55c0515d64b2a</t>
+          <t>327e928d80b137060bd55c0515d64b2a</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -24174,7 +24174,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>X64d94620fe0f5db1cd211f24f6a6d659</t>
+          <t>64d94620fe0f5db1cd211f24f6a6d659</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -24219,7 +24219,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>X94adac1e5690b5aef26d6014e471f458</t>
+          <t>94adac1e5690b5aef26d6014e471f458</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -24264,7 +24264,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Xdc04cb67b3295173275e20a8a7a3d16a</t>
+          <t>dc04cb67b3295173275e20a8a7a3d16a</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -24309,7 +24309,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>X19563b70bb3469c665c888e4685e7f99</t>
+          <t>19563b70bb3469c665c888e4685e7f99</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -24354,7 +24354,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>X7bf7ea59cac793e65c0bc293eabf44dc</t>
+          <t>7bf7ea59cac793e65c0bc293eabf44dc</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -24399,7 +24399,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>X8ac938c2111c4dea67b9a99a3f7900bc</t>
+          <t>8ac938c2111c4dea67b9a99a3f7900bc</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -24444,7 +24444,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Xfc4575c432e5f43c1eaf202f1c5816c4</t>
+          <t>fc4575c432e5f43c1eaf202f1c5816c4</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -24489,7 +24489,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>X6f0b4058c92e83c77533a218739a0e38</t>
+          <t>6f0b4058c92e83c77533a218739a0e38</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -24534,7 +24534,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Xc00514d54b15725f03c323c54796a7c0</t>
+          <t>c00514d54b15725f03c323c54796a7c0</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -24579,7 +24579,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>X2a7ee151e83dbc4a4ac13f84a434c8c7</t>
+          <t>2a7ee151e83dbc4a4ac13f84a434c8c7</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -24624,7 +24624,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>X970d6f0c54e1e999cbdcdefc80299e2b</t>
+          <t>970d6f0c54e1e999cbdcdefc80299e2b</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -24669,7 +24669,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Xf3e1ff3be3a6f13f24666ea97d99cd0b</t>
+          <t>f3e1ff3be3a6f13f24666ea97d99cd0b</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -24714,7 +24714,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>X7d0ccb9242c92ba67eae0552bf7c6f94</t>
+          <t>7d0ccb9242c92ba67eae0552bf7c6f94</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -24759,7 +24759,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Xe8d0f444dc3a43708bc843fd8472b381</t>
+          <t>e8d0f444dc3a43708bc843fd8472b381</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -24804,7 +24804,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Xe8d0f444dc3a43708bc843fd8472b381</t>
+          <t>e8d0f444dc3a43708bc843fd8472b381</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -24849,7 +24849,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Xa965d63a2b3f783b281a48f774847f29</t>
+          <t>a965d63a2b3f783b281a48f774847f29</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -24894,7 +24894,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>X57188cc28844564b611d3dd0d6e30de7</t>
+          <t>57188cc28844564b611d3dd0d6e30de7</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -24939,7 +24939,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>X76aa915543cd876d620ebeafeb9fd767</t>
+          <t>76aa915543cd876d620ebeafeb9fd767</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -24984,7 +24984,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>X570cad8230542ad8f2c032a719120bee</t>
+          <t>570cad8230542ad8f2c032a719120bee</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -25029,7 +25029,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>X64d94620fe0f5db1cd211f24f6a6d659</t>
+          <t>64d94620fe0f5db1cd211f24f6a6d659</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -25074,7 +25074,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Xa9625534f57e5ed4661782588cc20467</t>
+          <t>a9625534f57e5ed4661782588cc20467</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -25119,7 +25119,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Xac4a57c0c6ca41f976c5c914e25ed371</t>
+          <t>ac4a57c0c6ca41f976c5c914e25ed371</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -25164,7 +25164,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>X1703aefcb845a13faff8f80ea8265820</t>
+          <t>1703aefcb845a13faff8f80ea8265820</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -25209,7 +25209,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Xce7e172e3d64bc42dddb2f4aa26e3a03</t>
+          <t>ce7e172e3d64bc42dddb2f4aa26e3a03</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -25254,7 +25254,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>X47837e1a0b06f78d52ce1faf831fec84</t>
+          <t>47837e1a0b06f78d52ce1faf831fec84</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -25299,7 +25299,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>X059d6e79cba765d062053442b8ada21c</t>
+          <t>059d6e79cba765d062053442b8ada21c</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -25344,7 +25344,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>X79a123f051e7c2965a46226b1d95246e</t>
+          <t>79a123f051e7c2965a46226b1d95246e</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -25389,7 +25389,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>X9f185911874fb5d5b2623b647359f33b</t>
+          <t>9f185911874fb5d5b2623b647359f33b</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -25434,7 +25434,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>X94a45fbb634a4ae23f34d8160d95c8b7</t>
+          <t>94a45fbb634a4ae23f34d8160d95c8b7</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -25479,7 +25479,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>X4c089330a0f8ccdd7dd92492808e9247</t>
+          <t>4c089330a0f8ccdd7dd92492808e9247</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -25524,7 +25524,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>X6e373fe39ea68760cf9b2bf171476a55</t>
+          <t>6e373fe39ea68760cf9b2bf171476a55</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -25569,7 +25569,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>X9f05e4992392a05c38e1c790e07f3e5c</t>
+          <t>9f05e4992392a05c38e1c790e07f3e5c</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -25614,7 +25614,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>X18f3b811ae49dad2e01b20f5f39d10a7</t>
+          <t>18f3b811ae49dad2e01b20f5f39d10a7</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -25659,7 +25659,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>X86b5603a79c587d59312beef52df3409</t>
+          <t>86b5603a79c587d59312beef52df3409</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -25704,7 +25704,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Xc44642d31840ae8b6896c0bc0f5a8802</t>
+          <t>c44642d31840ae8b6896c0bc0f5a8802</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -25749,7 +25749,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Xa0ac269acfcd16c66700762ee6340b07</t>
+          <t>a0ac269acfcd16c66700762ee6340b07</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -25794,7 +25794,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>X9d2a55480c1cd54eacfb0243d4562261</t>
+          <t>9d2a55480c1cd54eacfb0243d4562261</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -25839,7 +25839,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Xa0f9d2150e3f8419a6ade2e296eafb5f</t>
+          <t>a0f9d2150e3f8419a6ade2e296eafb5f</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -25884,7 +25884,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>X77be5efca77e4204775e4e828a1580db</t>
+          <t>77be5efca77e4204775e4e828a1580db</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -25929,7 +25929,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>X0b3590ab4de6582222af6f3565ceca0c</t>
+          <t>0b3590ab4de6582222af6f3565ceca0c</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -25974,7 +25974,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Xc44642d31840ae8b6896c0bc0f5a8802</t>
+          <t>c44642d31840ae8b6896c0bc0f5a8802</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -26019,7 +26019,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>X1941bdf9450a85f4069a80e526137af7</t>
+          <t>1941bdf9450a85f4069a80e526137af7</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -26064,7 +26064,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>X1131f697b19dc061094f3b846b9f66a0</t>
+          <t>1131f697b19dc061094f3b846b9f66a0</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -26109,7 +26109,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>X194d511e554b455dac7747ef6442339f</t>
+          <t>194d511e554b455dac7747ef6442339f</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -26154,7 +26154,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>X3d514b698192fb4c2a0445c3498b2cfb</t>
+          <t>3d514b698192fb4c2a0445c3498b2cfb</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -26199,7 +26199,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Xa965d63a2b3f783b281a48f774847f29</t>
+          <t>a965d63a2b3f783b281a48f774847f29</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -26244,7 +26244,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>X059d6e79cba765d062053442b8ada21c</t>
+          <t>059d6e79cba765d062053442b8ada21c</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -26289,7 +26289,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>X9f79ff73dcbc3e304545d60cdbbca33b</t>
+          <t>9f79ff73dcbc3e304545d60cdbbca33b</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -26334,7 +26334,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Xa3d1f4355f204d4d49ad2bea3b801265</t>
+          <t>a3d1f4355f204d4d49ad2bea3b801265</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -26379,7 +26379,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Xfc2bf17d11280ea7e498670124f07400</t>
+          <t>fc2bf17d11280ea7e498670124f07400</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -26424,7 +26424,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Xfc2bf17d11280ea7e498670124f07400</t>
+          <t>fc2bf17d11280ea7e498670124f07400</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -26469,7 +26469,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>X4c089330a0f8ccdd7dd92492808e9247</t>
+          <t>4c089330a0f8ccdd7dd92492808e9247</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -26514,7 +26514,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Xa49ea569715664c78018691088f7aaac</t>
+          <t>a49ea569715664c78018691088f7aaac</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -26559,7 +26559,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Xa3d1f4355f204d4d49ad2bea3b801265</t>
+          <t>a3d1f4355f204d4d49ad2bea3b801265</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -26604,7 +26604,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>X19563b70bb3469c665c888e4685e7f99</t>
+          <t>19563b70bb3469c665c888e4685e7f99</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -26649,7 +26649,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>X19563b70bb3469c665c888e4685e7f99</t>
+          <t>19563b70bb3469c665c888e4685e7f99</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -26694,7 +26694,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>X1daf7490935642942f91e007dfefa7e9</t>
+          <t>1daf7490935642942f91e007dfefa7e9</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -26739,7 +26739,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>X77be5efca77e4204775e4e828a1580db</t>
+          <t>77be5efca77e4204775e4e828a1580db</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -26784,7 +26784,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>X00dcba6e262a3194c68f52e6af48a071</t>
+          <t>00dcba6e262a3194c68f52e6af48a071</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -26829,7 +26829,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Xe8d0f444dc3a43708bc843fd8472b381</t>
+          <t>e8d0f444dc3a43708bc843fd8472b381</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -26874,7 +26874,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>X1300fb2208dcbb54d400995de3bc2eaa</t>
+          <t>1300fb2208dcbb54d400995de3bc2eaa</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -26919,7 +26919,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>X182071d231a63cae957730240a214721</t>
+          <t>182071d231a63cae957730240a214721</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -26964,7 +26964,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Xc6b61011752152bbbc32003f5d0c5398</t>
+          <t>c6b61011752152bbbc32003f5d0c5398</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -27009,7 +27009,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>X7a6db5f059c69a310d7c97e1b488fe74</t>
+          <t>7a6db5f059c69a310d7c97e1b488fe74</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -27054,7 +27054,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Xf3270b7f9b020567e59ec30f7d15fc14</t>
+          <t>f3270b7f9b020567e59ec30f7d15fc14</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -27099,7 +27099,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>X2132a94c12039eca49c517950714e48a</t>
+          <t>2132a94c12039eca49c517950714e48a</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -27144,7 +27144,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>X64d94620fe0f5db1cd211f24f6a6d659</t>
+          <t>64d94620fe0f5db1cd211f24f6a6d659</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -27189,7 +27189,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>X327e928d80b137060bd55c0515d64b2a</t>
+          <t>327e928d80b137060bd55c0515d64b2a</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -27234,7 +27234,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>X84311c29ab5cf09c0720c450dc7c1a43</t>
+          <t>84311c29ab5cf09c0720c450dc7c1a43</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -27279,7 +27279,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>X860a5e9ee39ccb39131b57de03fb5bf8</t>
+          <t>860a5e9ee39ccb39131b57de03fb5bf8</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -27324,7 +27324,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>X6f0b4058c92e83c77533a218739a0e38</t>
+          <t>6f0b4058c92e83c77533a218739a0e38</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -27369,7 +27369,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Xc00514d54b15725f03c323c54796a7c0</t>
+          <t>c00514d54b15725f03c323c54796a7c0</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -27414,7 +27414,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>X64d94620fe0f5db1cd211f24f6a6d659</t>
+          <t>64d94620fe0f5db1cd211f24f6a6d659</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -27459,7 +27459,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>X1a9b1bbd7d800a46e40664e26298b33b</t>
+          <t>1a9b1bbd7d800a46e40664e26298b33b</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -27504,7 +27504,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>X3d514b698192fb4c2a0445c3498b2cfb</t>
+          <t>3d514b698192fb4c2a0445c3498b2cfb</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -27549,7 +27549,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Xa81bf36dba92ea8defbda21f3633f8fe</t>
+          <t>a81bf36dba92ea8defbda21f3633f8fe</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -27594,7 +27594,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Xecb427bf4473bf2f3205b06132125d07</t>
+          <t>ecb427bf4473bf2f3205b06132125d07</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -27639,7 +27639,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>X64d94620fe0f5db1cd211f24f6a6d659</t>
+          <t>64d94620fe0f5db1cd211f24f6a6d659</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -27684,7 +27684,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>X1a9b1bbd7d800a46e40664e26298b33b</t>
+          <t>1a9b1bbd7d800a46e40664e26298b33b</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -27729,7 +27729,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>X1e10ca4ce57e3019886b4f75360a76fa</t>
+          <t>1e10ca4ce57e3019886b4f75360a76fa</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -27774,7 +27774,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>X855166a7ea9905b7590e5e5fb7da7866</t>
+          <t>855166a7ea9905b7590e5e5fb7da7866</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -27819,7 +27819,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>X7ba07d9f4e22c332b04d5646fe2ea051</t>
+          <t>7ba07d9f4e22c332b04d5646fe2ea051</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -27864,7 +27864,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>X57188cc28844564b611d3dd0d6e30de7</t>
+          <t>57188cc28844564b611d3dd0d6e30de7</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -27909,7 +27909,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Xfc4575c432e5f43c1eaf202f1c5816c4</t>
+          <t>fc4575c432e5f43c1eaf202f1c5816c4</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -27954,7 +27954,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>X47837e1a0b06f78d52ce1faf831fec84</t>
+          <t>47837e1a0b06f78d52ce1faf831fec84</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -27999,7 +27999,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Xa0f9d2150e3f8419a6ade2e296eafb5f</t>
+          <t>a0f9d2150e3f8419a6ade2e296eafb5f</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -28044,7 +28044,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Xe8d0f444dc3a43708bc843fd8472b381</t>
+          <t>e8d0f444dc3a43708bc843fd8472b381</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -28089,7 +28089,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>X278651ccb0f0d07cd2ab0837262dfc39</t>
+          <t>278651ccb0f0d07cd2ab0837262dfc39</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -28134,7 +28134,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>Xa965d63a2b3f783b281a48f774847f29</t>
+          <t>a965d63a2b3f783b281a48f774847f29</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -28179,7 +28179,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>Xa81bf36dba92ea8defbda21f3633f8fe</t>
+          <t>a81bf36dba92ea8defbda21f3633f8fe</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -28224,7 +28224,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>X4c089330a0f8ccdd7dd92492808e9247</t>
+          <t>4c089330a0f8ccdd7dd92492808e9247</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -28269,7 +28269,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>X18f3b811ae49dad2e01b20f5f39d10a7</t>
+          <t>18f3b811ae49dad2e01b20f5f39d10a7</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -28314,7 +28314,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Xf3e1ff3be3a6f13f24666ea97d99cd0b</t>
+          <t>f3e1ff3be3a6f13f24666ea97d99cd0b</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -28359,7 +28359,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>X7bf7ea59cac793e65c0bc293eabf44dc</t>
+          <t>7bf7ea59cac793e65c0bc293eabf44dc</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -28404,7 +28404,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>X76214bb13d1e7d69ca2f7827e3ac12e2</t>
+          <t>76214bb13d1e7d69ca2f7827e3ac12e2</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -28449,7 +28449,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>X1e10ca4ce57e3019886b4f75360a76fa</t>
+          <t>1e10ca4ce57e3019886b4f75360a76fa</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -28494,7 +28494,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Xe52994cd67774b8f72113d04a0b2c493</t>
+          <t>e52994cd67774b8f72113d04a0b2c493</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -28539,7 +28539,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>X269fea3886e14ab0acb08ade901906fd</t>
+          <t>269fea3886e14ab0acb08ade901906fd</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -28584,7 +28584,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>X6e373fe39ea68760cf9b2bf171476a55</t>
+          <t>6e373fe39ea68760cf9b2bf171476a55</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -28629,7 +28629,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>X76d6be90e19a660c9a84b35fa31d801c</t>
+          <t>76d6be90e19a660c9a84b35fa31d801c</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -28674,7 +28674,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>X5c7f516ff4d244a8f63e883a44267f20</t>
+          <t>5c7f516ff4d244a8f63e883a44267f20</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -28719,7 +28719,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>X57188cc28844564b611d3dd0d6e30de7</t>
+          <t>57188cc28844564b611d3dd0d6e30de7</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -28764,7 +28764,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Xfc4575c432e5f43c1eaf202f1c5816c4</t>
+          <t>fc4575c432e5f43c1eaf202f1c5816c4</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -28809,7 +28809,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>X860a5e9ee39ccb39131b57de03fb5bf8</t>
+          <t>860a5e9ee39ccb39131b57de03fb5bf8</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -28854,7 +28854,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>X5b73138c8555560a7cd45cb7bd7ca6da</t>
+          <t>5b73138c8555560a7cd45cb7bd7ca6da</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -28899,7 +28899,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>X9d7e2f75c0754a3aaf6bf21a479a0046</t>
+          <t>9d7e2f75c0754a3aaf6bf21a479a0046</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -28944,7 +28944,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Xce7e172e3d64bc42dddb2f4aa26e3a03</t>
+          <t>ce7e172e3d64bc42dddb2f4aa26e3a03</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -28989,7 +28989,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>X2a7ee151e83dbc4a4ac13f84a434c8c7</t>
+          <t>2a7ee151e83dbc4a4ac13f84a434c8c7</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -29034,7 +29034,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>Xf3e1ff3be3a6f13f24666ea97d99cd0b</t>
+          <t>f3e1ff3be3a6f13f24666ea97d99cd0b</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -29079,7 +29079,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>X85c51ab58e3beec0355a935d17f0758e</t>
+          <t>85c51ab58e3beec0355a935d17f0758e</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -29124,7 +29124,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>X278651ccb0f0d07cd2ab0837262dfc39</t>
+          <t>278651ccb0f0d07cd2ab0837262dfc39</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -29169,7 +29169,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>X7ba07d9f4e22c332b04d5646fe2ea051</t>
+          <t>7ba07d9f4e22c332b04d5646fe2ea051</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -29214,7 +29214,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>Xc71265e180d7e06bd350017b893ea44a</t>
+          <t>c71265e180d7e06bd350017b893ea44a</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -29259,7 +29259,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>X61d6589645d112c45ea0478e6445fa34</t>
+          <t>61d6589645d112c45ea0478e6445fa34</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -29304,7 +29304,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>X96c7cedbae877361d087a8b39206d408</t>
+          <t>96c7cedbae877361d087a8b39206d408</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -29349,7 +29349,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>X0b2e7a7da00f71987193e385a9a4a4d1</t>
+          <t>0b2e7a7da00f71987193e385a9a4a4d1</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -29394,7 +29394,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>X2132a94c12039eca49c517950714e48a</t>
+          <t>2132a94c12039eca49c517950714e48a</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
